--- a/Replace.xlsx
+++ b/Replace.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python\Rag_0.14\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python\LLM_with_RAG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC823893-E094-4181-9650-75ED3ADFD430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990B14BB-684F-432B-A82E-F15842E6BA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Replace.xlsx
+++ b/Replace.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python\NLP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF394754-66A0-47C1-9931-7BEFDC9F93F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6BA5F3-BF2B-48B0-86F5-A0D715FEF460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="报告" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
     <sheet name="条件" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">报告!$A$1:$B$332</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">报告!$A$1:$B$329</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="1124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="1130">
   <si>
     <t>原始值</t>
   </si>
@@ -4247,6 +4247,29 @@
   <si>
     <t>胰腺头部</t>
     <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>T管造影</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>胆道T管造影</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ｔ管造影</t>
+  </si>
+  <si>
+    <t>前庭蜗神经</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>前庭神经、蜗神经</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>前庭、蜗神经</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4701,7 +4724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B515"/>
+  <dimension ref="A1:B516"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.875" customWidth="1"/>
@@ -6144,913 +6167,913 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A181" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>164</v>
+        <v>586</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A182" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.15">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A184" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>586</v>
+        <v>172</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A185" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A186" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A187" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A188" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
+      </c>
+      <c r="B188" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A189" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A190" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A191" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B191" t="s">
-        <v>180</v>
+        <v>185</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A192" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
+      </c>
+      <c r="B192" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A193" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A194" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A195" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A196" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A197" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>192</v>
+        <v>197</v>
+      </c>
+      <c r="B197" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A198" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B198" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A199" s="1" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A200" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B200" t="s">
-        <v>198</v>
+        <v>201</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A201" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B201" t="s">
-        <v>180</v>
+        <v>202</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A202" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
+      </c>
+      <c r="B202" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A203" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A204" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A205" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B205" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A206" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A207" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>192</v>
+        <v>208</v>
+      </c>
+      <c r="B207" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A208" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B208" t="s">
-        <v>194</v>
+      <c r="A208" t="s">
+        <v>209</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A209" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A210" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B210" t="s">
-        <v>198</v>
+        <v>213</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A211" t="s">
-        <v>209</v>
+      <c r="A211" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A212" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A213" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
+      </c>
+      <c r="B213" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A214" s="1" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A215" s="1" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A216" s="1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B216" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A217" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A218" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A219" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B219" t="s">
-        <v>226</v>
+        <v>231</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A220" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>228</v>
+        <v>66</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A221" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A222" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>21</v>
+        <v>236</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A223" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>66</v>
+        <v>238</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A224" s="1" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>234</v>
+        <v>546</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A225" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>236</v>
+        <v>546</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A226" s="1" t="s">
-        <v>237</v>
+        <v>803</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A227" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>546</v>
+        <v>246</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A228" s="1" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>546</v>
+        <v>248</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A229" s="1" t="s">
-        <v>803</v>
+        <v>898</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>241</v>
+        <v>899</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A230" s="1" t="s">
-        <v>245</v>
+        <v>900</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>246</v>
+        <v>899</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A231" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>248</v>
+      <c r="A231" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A232" s="1" t="s">
-        <v>898</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>899</v>
+      <c r="A232" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A233" s="1" t="s">
-        <v>900</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>899</v>
+      <c r="A233" t="s">
+        <v>251</v>
+      </c>
+      <c r="B233" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A234" t="s">
-        <v>249</v>
+        <v>253</v>
+      </c>
+      <c r="B234" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A235" t="s">
-        <v>250</v>
+        <v>254</v>
+      </c>
+      <c r="B235" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A236" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B236" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A237" t="s">
-        <v>253</v>
+      <c r="A237" s="1" t="s">
+        <v>804</v>
       </c>
       <c r="B237" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A238" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="B238" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A239" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="B239" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A240" s="1" t="s">
-        <v>804</v>
+      <c r="A240" t="s">
+        <v>268</v>
       </c>
       <c r="B240" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A241" t="s">
-        <v>264</v>
-      </c>
-      <c r="B241" t="s">
-        <v>265</v>
+        <v>270</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>829</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A242" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B242" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A243" t="s">
-        <v>268</v>
-      </c>
-      <c r="B243" t="s">
-        <v>269</v>
+        <v>273</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A244" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>829</v>
+        <v>274</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A245" t="s">
-        <v>271</v>
-      </c>
-      <c r="B245" t="s">
-        <v>272</v>
+        <v>276</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A246" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A247" t="s">
-        <v>275</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A248" t="s">
-        <v>276</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>277</v>
+      <c r="A248" s="3" t="s">
+        <v>1011</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A249" t="s">
-        <v>278</v>
-      </c>
-      <c r="B249" s="1" t="s">
-        <v>277</v>
+      <c r="A249" s="3" t="s">
+        <v>1016</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A250" t="s">
-        <v>279</v>
+      <c r="A250" s="3" t="s">
+        <v>1012</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A251" s="3" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A252" s="3" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A253" s="3" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A254" s="3" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A255" s="3" t="s">
-        <v>1014</v>
+        <v>280</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A256" s="3" t="s">
-        <v>1015</v>
+        <v>281</v>
+      </c>
+      <c r="B256" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A257" s="3" t="s">
-        <v>1010</v>
+        <v>283</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A258" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
+      </c>
+      <c r="B258" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A259" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B259" t="s">
-        <v>282</v>
+        <v>286</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A260" s="3" t="s">
-        <v>283</v>
+        <v>288</v>
+      </c>
+      <c r="B260" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A261" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B261" t="s">
-        <v>285</v>
+        <v>290</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A262" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
+      </c>
+      <c r="B262" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A263" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B263" t="s">
-        <v>289</v>
+        <v>295</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A264" s="3" t="s">
-        <v>290</v>
+        <v>780</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>291</v>
+        <v>805</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A265" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B265" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A266" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>805</v>
+        <v>297</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A267" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="B267" s="1" t="s">
-        <v>805</v>
+        <v>298</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A268" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A269" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
+      </c>
+      <c r="B269" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A270" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
+      </c>
+      <c r="B270" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A271" s="3" t="s">
-        <v>299</v>
+        <v>882</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A272" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B272" t="s">
-        <v>301</v>
+      <c r="A272" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A273" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B273" t="s">
-        <v>303</v>
+        <v>550</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A274" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="B274" s="1" t="s">
-        <v>478</v>
+        <v>306</v>
+      </c>
+      <c r="B274" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A275" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="B275" s="1" t="s">
-        <v>478</v>
+      <c r="A275" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B275" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A276" s="3" t="s">
-        <v>550</v>
+        <v>790</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>478</v>
+        <v>792</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A277" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B277" t="s">
-        <v>307</v>
+        <v>791</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A278" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="B278" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A279" s="3" t="s">
-        <v>790</v>
+        <v>314</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>792</v>
+        <v>315</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A280" s="3" t="s">
-        <v>791</v>
+        <v>316</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>792</v>
+        <v>317</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A281" s="3" t="s">
-        <v>311</v>
+        <v>318</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A282" s="3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A283" s="3" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A284" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A285" s="3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A286" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A287" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B287" s="1" t="s">
-        <v>325</v>
+      <c r="A287" t="s">
+        <v>328</v>
+      </c>
+      <c r="B287" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A288" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B288" s="1" t="s">
-        <v>325</v>
+      <c r="A288" t="s">
+        <v>330</v>
+      </c>
+      <c r="B288" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A289" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A290" t="s">
-        <v>328</v>
-      </c>
-      <c r="B290" t="s">
-        <v>329</v>
+      <c r="A290" s="3" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A291" t="s">
-        <v>330</v>
-      </c>
-      <c r="B291" t="s">
-        <v>331</v>
+      <c r="A291" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A292" s="3" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A293" s="3" t="s">
-        <v>334</v>
+        <v>611</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A294" s="3" t="s">
-        <v>339</v>
+        <v>609</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>340</v>
+        <v>610</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A295" s="3" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A296" s="3" t="s">
-        <v>611</v>
+        <v>337</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>610</v>
+        <v>338</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A297" s="3" t="s">
-        <v>609</v>
+        <v>342</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A298" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A298" s="4" t="s">
+        <v>344</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>336</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A299" s="3" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>338</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A300" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="301" spans="1:2" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A301" s="4" t="s">
-        <v>344</v>
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A301" s="3" t="s">
+        <v>347</v>
       </c>
       <c r="B301" s="1" t="s">
         <v>1091</v>
@@ -7058,524 +7081,524 @@
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A302" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>1091</v>
+        <v>349</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A303" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>1091</v>
+        <v>349</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A304" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1091</v>
+        <v>352</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A305" s="3" t="s">
-        <v>348</v>
+      <c r="A305" t="s">
+        <v>353</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A306" s="3" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A307" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B307" s="1" t="s">
-        <v>352</v>
+      <c r="A307" t="s">
+        <v>356</v>
+      </c>
+      <c r="B307" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A308" t="s">
-        <v>353</v>
-      </c>
-      <c r="B308" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A309" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="B309" s="1" t="s">
-        <v>354</v>
+      <c r="A309" t="s">
+        <v>359</v>
+      </c>
+      <c r="B309" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A310" t="s">
-        <v>356</v>
-      </c>
-      <c r="B310" t="s">
-        <v>357</v>
+      <c r="A310" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A311" t="s">
-        <v>358</v>
+      <c r="A311" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A312" t="s">
-        <v>359</v>
-      </c>
-      <c r="B312" t="s">
-        <v>360</v>
+      <c r="A312" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A313" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A314" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="B314" s="1" t="s">
-        <v>774</v>
+      <c r="A314" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A315" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="B315" s="1" t="s">
-        <v>774</v>
+      <c r="A315" t="s">
+        <v>374</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A316" s="5" t="s">
-        <v>369</v>
+      <c r="A316" s="1" t="s">
+        <v>858</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A317" s="5" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A318" t="s">
-        <v>374</v>
-      </c>
-      <c r="B318" s="5" t="s">
-        <v>375</v>
+      <c r="A318" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>859</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A319" s="1" t="s">
-        <v>858</v>
+      <c r="A319" s="5" t="s">
+        <v>378</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A320" s="5" t="s">
-        <v>376</v>
+      <c r="A320" t="s">
+        <v>379</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A321" s="1" t="s">
-        <v>144</v>
+        <v>382</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>859</v>
+        <v>383</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A322" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="B322" s="5" t="s">
-        <v>380</v>
+      <c r="A322" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A323" t="s">
-        <v>379</v>
-      </c>
-      <c r="B323" s="5" t="s">
-        <v>381</v>
+      <c r="A323" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A324" s="1" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A325" s="1" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A326" s="1" t="s">
-        <v>386</v>
+      <c r="A326" t="s">
+        <v>394</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A327" s="1" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A328" s="1" t="s">
-        <v>392</v>
+      <c r="A328" t="s">
+        <v>397</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>393</v>
+        <v>776</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A329" t="s">
-        <v>394</v>
+      <c r="A329" s="1" t="s">
+        <v>398</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>395</v>
+        <v>777</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A330" s="1" t="s">
-        <v>396</v>
+        <v>428</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A331" t="s">
-        <v>397</v>
+      <c r="A331" s="1" t="s">
+        <v>438</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>776</v>
+        <v>450</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A332" s="1" t="s">
-        <v>398</v>
+        <v>439</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>777</v>
+        <v>451</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A333" s="1" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A334" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A335" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A336" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A337" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A338" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A339" s="1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A340" s="1" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A341" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A342" s="1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A343" s="1" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A344" s="1" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A345" s="1" t="s">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A346" s="1" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A347" s="1" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A348" s="1" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A349" s="1" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A350" s="1" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A351" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A352" s="1" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A353" s="1" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A354" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A355" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A356" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A357" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A358" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A359" s="1" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A360" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A361" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.15">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" ht="15" x14ac:dyDescent="0.15">
       <c r="A362" s="1" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A363" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A364" s="1" t="s">
-        <v>501</v>
+        <v>529</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="365" spans="1:2" ht="15" x14ac:dyDescent="0.15">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A365" s="1" t="s">
-        <v>503</v>
+        <v>570</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>502</v>
+        <v>571</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A366" s="1" t="s">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>506</v>
+        <v>530</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A367" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>530</v>
@@ -7583,15 +7606,15 @@
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A368" s="1" t="s">
-        <v>570</v>
+        <v>533</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>571</v>
+        <v>530</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A369" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>530</v>
@@ -7599,7 +7622,7 @@
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A370" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>530</v>
@@ -7607,7 +7630,7 @@
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A371" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>530</v>
@@ -7615,615 +7638,615 @@
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A372" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="B372" s="1" t="s">
-        <v>530</v>
+        <v>673</v>
+      </c>
+      <c r="B372" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A373" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A374" s="1" t="s">
-        <v>536</v>
+        <v>568</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>530</v>
+        <v>569</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A375" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="B375" t="s">
-        <v>537</v>
+        <v>573</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A376" s="1" t="s">
-        <v>538</v>
+      <c r="A376" t="s">
+        <v>575</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A377" s="1" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A378" s="1" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A379" t="s">
-        <v>575</v>
+      <c r="A379" s="1" t="s">
+        <v>581</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A380" s="1" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A381" s="1" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>580</v>
+        <v>806</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A382" s="1" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>582</v>
+        <v>592</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A383" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A384" s="1" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>806</v>
+        <v>601</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A385" s="1" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A386" s="1" t="s">
-        <v>593</v>
+        <v>612</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>594</v>
+        <v>613</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A387" s="1" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>601</v>
+        <v>615</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A388" s="1" t="s">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A389" s="1" t="s">
-        <v>612</v>
+        <v>629</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>613</v>
+        <v>630</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A390" s="1" t="s">
-        <v>614</v>
+        <v>631</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>615</v>
+        <v>630</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A391" s="1" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>617</v>
+        <v>633</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A392" s="1" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>630</v>
+        <v>648</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A393" s="1" t="s">
-        <v>631</v>
+        <v>716</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>630</v>
+        <v>717</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A394" s="1" t="s">
-        <v>632</v>
+        <v>718</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>633</v>
+        <v>719</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A395" s="1" t="s">
-        <v>647</v>
+        <v>897</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>648</v>
+        <v>719</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A396" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A397" s="1" t="s">
-        <v>718</v>
+        <v>901</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A398" s="1" t="s">
-        <v>897</v>
+        <v>749</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>719</v>
+        <v>420</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A399" s="1" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A400" s="1" t="s">
-        <v>901</v>
+        <v>725</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A401" s="1" t="s">
-        <v>749</v>
+        <v>727</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>420</v>
+        <v>728</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A402" s="1" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>724</v>
+        <v>735</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A403" s="1" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A404" s="1" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>728</v>
+        <v>737</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A405" s="1" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A406" s="1" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A407" s="1" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.15">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A408" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="B408" s="1" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.15">
+        <v>741</v>
+      </c>
+      <c r="B408" s="6" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A409" s="1" t="s">
-        <v>729</v>
+        <v>742</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.15">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A410" s="1" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
     </row>
     <row r="411" spans="1:2" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A411" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="B411" s="6" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="412" spans="1:2" ht="16.5" x14ac:dyDescent="0.15">
+        <v>744</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A412" s="1" t="s">
-        <v>742</v>
+        <v>760</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="413" spans="1:2" ht="16.5" x14ac:dyDescent="0.15">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A413" s="1" t="s">
-        <v>743</v>
+        <v>762</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="414" spans="1:2" ht="16.5" x14ac:dyDescent="0.15">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A414" s="1" t="s">
-        <v>744</v>
+        <v>763</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>748</v>
+        <v>764</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A415" s="1" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A416" s="1" t="s">
-        <v>762</v>
+        <v>778</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>765</v>
+        <v>779</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A417" s="1" t="s">
-        <v>763</v>
+        <v>782</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>764</v>
+        <v>781</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A418" s="1" t="s">
-        <v>766</v>
+        <v>783</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>767</v>
+        <v>781</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A419" s="1" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A420" s="1" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A421" s="1" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A422" s="1" t="s">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A423" s="1" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>787</v>
+        <v>798</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A424" s="1" t="s">
-        <v>788</v>
+        <v>801</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>789</v>
+        <v>802</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A425" s="1" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A426" s="1" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A427" s="1" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A428" s="1" t="s">
-        <v>795</v>
+        <v>811</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>799</v>
+        <v>815</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A429" s="1" t="s">
-        <v>796</v>
+        <v>812</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>800</v>
+        <v>816</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A430" s="1" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A431" s="1" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A432" s="1" t="s">
-        <v>812</v>
+        <v>821</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A433" s="1" t="s">
-        <v>813</v>
+        <v>823</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A434" s="1" t="s">
-        <v>814</v>
+        <v>825</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A435" s="1" t="s">
-        <v>821</v>
+      <c r="A435" t="s">
+        <v>856</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>822</v>
+        <v>857</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A436" s="1" t="s">
-        <v>823</v>
+        <v>860</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>824</v>
+        <v>861</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A437" s="1" t="s">
-        <v>825</v>
+        <v>870</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>826</v>
+        <v>871</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A438" t="s">
-        <v>856</v>
+      <c r="A438" s="1" t="s">
+        <v>872</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>857</v>
+        <v>874</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A439" s="1" t="s">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>861</v>
+        <v>875</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A440" s="1" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A441" s="1" t="s">
-        <v>872</v>
+        <v>885</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A442" s="1" t="s">
-        <v>873</v>
+        <v>891</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>875</v>
+        <v>892</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A443" s="1" t="s">
-        <v>876</v>
+      <c r="A443" t="s">
+        <v>894</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>877</v>
+        <v>896</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A444" s="1" t="s">
-        <v>885</v>
+        <v>895</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>886</v>
+        <v>896</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A445" s="1" t="s">
+      <c r="A445" t="s">
+        <v>902</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A446" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="B445" s="1" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A446" t="s">
-        <v>894</v>
-      </c>
       <c r="B446" s="1" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A447" s="1" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A448" t="s">
-        <v>902</v>
+      <c r="A448" s="1" t="s">
+        <v>904</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>890</v>
@@ -8231,415 +8254,415 @@
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A449" s="1" t="s">
-        <v>891</v>
+        <v>907</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A450" s="1" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>890</v>
+        <v>910</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A451" s="1" t="s">
-        <v>904</v>
+        <v>1026</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>890</v>
+        <v>912</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A452" s="1" t="s">
-        <v>907</v>
+      <c r="A452" t="s">
+        <v>911</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A453" s="1" t="s">
-        <v>908</v>
+        <v>1027</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A454" s="1" t="s">
-        <v>1026</v>
+      <c r="A454" t="s">
+        <v>919</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A455" t="s">
-        <v>911</v>
+        <v>921</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>912</v>
+        <v>922</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A456" s="1" t="s">
-        <v>1027</v>
+      <c r="A456" t="s">
+        <v>923</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A457" t="s">
-        <v>919</v>
+      <c r="A457" s="1" t="s">
+        <v>925</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A458" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A459" t="s">
-        <v>923</v>
+      <c r="A459" s="1" t="s">
+        <v>928</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A460" s="1" t="s">
-        <v>925</v>
+      <c r="A460" t="s">
+        <v>931</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A461" t="s">
-        <v>927</v>
+      <c r="A461" s="1" t="s">
+        <v>933</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A462" s="1" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A463" t="s">
-        <v>931</v>
+      <c r="A463" s="1" t="s">
+        <v>935</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A464" s="1" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A465" s="1" t="s">
-        <v>934</v>
+      <c r="A465" t="s">
+        <v>941</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A466" s="1" t="s">
-        <v>935</v>
+      <c r="A466" t="s">
+        <v>943</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A467" s="1" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A468" t="s">
-        <v>941</v>
+      <c r="A468" s="1" t="s">
+        <v>947</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A469" t="s">
-        <v>943</v>
+      <c r="A469" s="1" t="s">
+        <v>949</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A470" s="1" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A471" s="1" t="s">
-        <v>947</v>
+      <c r="A471" t="s">
+        <v>953</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A472" s="1" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A473" s="1" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A474" t="s">
-        <v>953</v>
+        <v>970</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>954</v>
+        <v>886</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A475" s="1" t="s">
-        <v>955</v>
+      <c r="A475" t="s">
+        <v>973</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>954</v>
+        <v>974</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A476" s="1" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>957</v>
+        <v>978</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A477" t="s">
-        <v>970</v>
+      <c r="A477" s="1" t="s">
+        <v>979</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>886</v>
+        <v>980</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A478" t="s">
-        <v>973</v>
+      <c r="A478" s="1" t="s">
+        <v>981</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A479" s="1" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A480" s="1" t="s">
-        <v>979</v>
+      <c r="A480" t="s">
+        <v>983</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A481" s="1" t="s">
-        <v>981</v>
+      <c r="A481" t="s">
+        <v>985</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A482" s="1" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A483" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A484" t="s">
-        <v>985</v>
+      <c r="A484" s="1" t="s">
+        <v>993</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A485" s="1" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>986</v>
+        <v>996</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A486" t="s">
-        <v>991</v>
+      <c r="A486" s="1" t="s">
+        <v>995</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A487" s="1" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>992</v>
+        <v>999</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A488" s="1" t="s">
-        <v>994</v>
+      <c r="A488" t="s">
+        <v>1000</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A489" s="1" t="s">
-        <v>995</v>
+        <v>1018</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>997</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A490" s="1" t="s">
-        <v>998</v>
+        <v>1020</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>999</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A491" t="s">
-        <v>1000</v>
+      <c r="A491" s="1" t="s">
+        <v>1028</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>1001</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A492" s="1" t="s">
-        <v>1018</v>
+        <v>1030</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>1019</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A493" s="1" t="s">
-        <v>1020</v>
+        <v>1032</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>1021</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A494" s="1" t="s">
-        <v>1028</v>
+        <v>1035</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>1029</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A495" s="1" t="s">
-        <v>1030</v>
+        <v>836</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>1031</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A496" s="1" t="s">
-        <v>1032</v>
+        <v>1088</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>1033</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A497" s="1" t="s">
-        <v>1035</v>
+      <c r="A497" t="s">
+        <v>1081</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>1036</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A498" s="1" t="s">
-        <v>836</v>
+        <v>1083</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A499" s="1" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A500" t="s">
-        <v>1081</v>
+      <c r="A500" s="1" t="s">
+        <v>1085</v>
       </c>
       <c r="B500" s="1" t="s">
         <v>1082</v>
@@ -8647,120 +8670,128 @@
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A501" s="1" t="s">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>1082</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A502" s="1" t="s">
-        <v>1084</v>
+      <c r="A502" t="s">
+        <v>1094</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A503" s="1" t="s">
-        <v>1085</v>
+      <c r="A503" t="s">
+        <v>1096</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>1082</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A504" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="B504" s="1" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A505" t="s">
-        <v>1094</v>
-      </c>
-      <c r="B505" s="1" t="s">
-        <v>1095</v>
+      <c r="A505" s="1" t="s">
+        <v>1101</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A506" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A507" s="1" t="s">
-        <v>1100</v>
+        <v>1106</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>1107</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A508" s="1" t="s">
-        <v>1101</v>
+      <c r="A508" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B508" s="1" t="s">
+        <v>1113</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A509" t="s">
-        <v>1104</v>
+      <c r="A509" s="1" t="s">
+        <v>1114</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A510" s="1" t="s">
-        <v>1106</v>
+        <v>1115</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>1107</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A511" t="s">
-        <v>1112</v>
+      <c r="A511" s="1" t="s">
+        <v>1117</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A512" s="1" t="s">
-        <v>1114</v>
+      <c r="A512" t="s">
+        <v>1110</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A513" s="1" t="s">
-        <v>1115</v>
+        <v>1124</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>1116</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A514" s="1" t="s">
-        <v>1117</v>
+      <c r="A514" t="s">
+        <v>1126</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>1116</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A515" t="s">
-        <v>1110</v>
+      <c r="A515" s="1" t="s">
+        <v>1127</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>1111</v>
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A516" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>1128</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B332" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:B329" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
